--- a/output/sliding_window_results_window_9.xlsx
+++ b/output/sliding_window_results_window_9.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.04559863387234</v>
+        <v>51.45668943985095</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.054401366127657</v>
+        <v>3.356689439850946</v>
       </c>
       <c r="E2" t="n">
-        <v>1.111762240891868</v>
+        <v>11.26736399560686</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>33.77052532786719</v>
+        <v>56.24915069150725</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6294746721328082</v>
+        <v>3.249150691507253</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3962383628567063</v>
+        <v>10.55698021612206</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C4" t="n">
-        <v>35.27402026334813</v>
+        <v>62.50259291215355</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.025979736651863</v>
+        <v>6.402592912153551</v>
       </c>
       <c r="E4" t="n">
-        <v>1.052634420020225</v>
+        <v>40.99319599875889</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>36.54584430169669</v>
+        <v>64.1674321101296</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.95415569830331</v>
+        <v>4.167432110129596</v>
       </c>
       <c r="E5" t="n">
-        <v>3.818724493211298</v>
+        <v>17.36749039253922</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C6" t="n">
-        <v>38.3724097597778</v>
+        <v>71.2470736002893</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.727590240222206</v>
+        <v>7.347073600289299</v>
       </c>
       <c r="E6" t="n">
-        <v>2.984568038111019</v>
+        <v>53.97949048806797</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>39.94324303117602</v>
+        <v>77.29301163149944</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.556756968823983</v>
+        <v>6.693011631499445</v>
       </c>
       <c r="E7" t="n">
-        <v>2.423492259982035</v>
+        <v>44.79640469938686</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>43.4383173806476</v>
+        <v>86.74475078806347</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2616826193523991</v>
+        <v>5.844750788063465</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06847779327113261</v>
+        <v>34.16111177456849</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>44.8290802083585</v>
+        <v>94.57382127951041</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.270919791641496</v>
+        <v>5.473821279510418</v>
       </c>
       <c r="E9" t="n">
-        <v>10.69891628335205</v>
+        <v>29.96271940002107</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C10" t="n">
-        <v>49.0935642328113</v>
+        <v>87.33236681589456</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.906435767188697</v>
+        <v>-7.667633184105441</v>
       </c>
       <c r="E10" t="n">
-        <v>15.26024040317114</v>
+        <v>58.79259864599494</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C11" t="n">
-        <v>53.87625568250802</v>
+        <v>100.0249853600868</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.223744317491985</v>
+        <v>1.224985360086791</v>
       </c>
       <c r="E11" t="n">
-        <v>4.945038789577892</v>
+        <v>1.500589132426965</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C12" t="n">
-        <v>57.61948349648057</v>
+        <v>104.7060249114565</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.380516503519431</v>
+        <v>1.40602491145647</v>
       </c>
       <c r="E12" t="n">
-        <v>5.666858823528376</v>
+        <v>1.976906051636174</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>60.86752445642613</v>
+        <v>114.6910655564132</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.032475543573867</v>
+        <v>7.691065556413236</v>
       </c>
       <c r="E13" t="n">
-        <v>9.195907922373618</v>
+        <v>59.15248939304603</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C14" t="n">
-        <v>68.46807069093819</v>
+        <v>121.2693368705412</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.131929309061803</v>
+        <v>12.56933687054122</v>
       </c>
       <c r="E14" t="n">
-        <v>4.545122578836738</v>
+        <v>157.988229365147</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C15" t="n">
-        <v>75.88599941867363</v>
+        <v>122.6052483351502</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.014000581326371</v>
+        <v>9.905248335150205</v>
       </c>
       <c r="E15" t="n">
-        <v>25.14020182954119</v>
+        <v>98.11394458099591</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C16" t="n">
-        <v>84.23136670986639</v>
+        <v>127.5438953478685</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.868633290133602</v>
+        <v>10.34389534786845</v>
       </c>
       <c r="E16" t="n">
-        <v>23.70359011379714</v>
+        <v>106.9961709676546</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C17" t="n">
-        <v>89.87644944011652</v>
+        <v>128.3580029161565</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.123550559883483</v>
+        <v>5.258002916156471</v>
       </c>
       <c r="E17" t="n">
-        <v>26.25077033968236</v>
+        <v>27.64659466630995</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>98.8</v>
+        <v>128.9</v>
       </c>
       <c r="C18" t="n">
-        <v>94.59565316417002</v>
+        <v>130.3230597200969</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.20434683582998</v>
+        <v>1.423059720096887</v>
       </c>
       <c r="E18" t="n">
-        <v>17.67653231595357</v>
+        <v>2.025098966962231</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>103.3</v>
+        <v>135.1</v>
       </c>
       <c r="C19" t="n">
-        <v>99.40219775248991</v>
+        <v>138.0058861954278</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.897802247510086</v>
+        <v>2.905886195427854</v>
       </c>
       <c r="E19" t="n">
-        <v>15.19286236069468</v>
+        <v>8.444174580778169</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>107</v>
+        <v>139.4</v>
       </c>
       <c r="C20" t="n">
-        <v>101.7896607657903</v>
+        <v>143.4589015334267</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.21033923420967</v>
+        <v>4.058901533426706</v>
       </c>
       <c r="E20" t="n">
-        <v>27.14763493554461</v>
+        <v>16.47468165805367</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>108.7</v>
+        <v>143.8</v>
       </c>
       <c r="C21" t="n">
-        <v>105.2807651912938</v>
+        <v>152.6413451032639</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.419234808706179</v>
+        <v>8.841345103263848</v>
       </c>
       <c r="E21" t="n">
-        <v>11.69116667706798</v>
+        <v>78.16938323500761</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-56.89397009169087</v>
+        <v>100.4946411187867</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>208.9707409814656</v>
+        <v>860.3656182090847</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>10.44853704907328</v>
+        <v>43.01828091045424</v>
       </c>
     </row>
   </sheetData>
